--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,6 +1115,148 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130335787</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hässjemossen, Hässjemossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497328</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6587874</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130335807</v>
       </c>
       <c r="B5" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130335710</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130336577</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130335671</v>
       </c>
       <c r="B4" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130335807</v>
       </c>
       <c r="B5" t="n">
-        <v>91682</v>
+        <v>91708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130335787</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130335807</v>
       </c>
       <c r="B5" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130335807</v>
       </c>
       <c r="B5" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130335710</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130336577</v>
       </c>
       <c r="B3" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130335671</v>
       </c>
       <c r="B4" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130335807</v>
       </c>
       <c r="B5" t="n">
-        <v>91710</v>
+        <v>91712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130335787</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -787,53 +787,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130336577</v>
+        <v>130335807</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>91712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hässjemossen, Hässjemossen, Vstm</t>
+          <t>Lofallskullen, Lofallskullen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497453</v>
+        <v>497270</v>
       </c>
       <c r="R3" t="n">
-        <v>6587634</v>
+        <v>6587896</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +858,14 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:01</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,56 +874,57 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335671</v>
+        <v>130335787</v>
       </c>
       <c r="B4" t="n">
-        <v>57044</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497291</v>
+        <v>497328</v>
       </c>
       <c r="R4" t="n">
-        <v>6587789</v>
+        <v>6587874</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +978,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,67 +994,94 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130335807</v>
+        <v>130336577</v>
       </c>
       <c r="B5" t="n">
-        <v>91712</v>
+        <v>57044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lofallskullen, Lofallskullen, Vstm</t>
+          <t>Hässjemossen, Hässjemossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497270</v>
+        <v>497453</v>
       </c>
       <c r="R5" t="n">
-        <v>6587896</v>
+        <v>6587634</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,14 +1108,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,57 +1129,56 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335787</v>
+        <v>130335671</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1157,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497328</v>
+        <v>497291</v>
       </c>
       <c r="R6" t="n">
-        <v>6587874</v>
+        <v>6587789</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,41 +1243,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130335710</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130335807</v>
       </c>
       <c r="B3" t="n">
-        <v>91712</v>
+        <v>91724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130335787</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>130336577</v>
       </c>
       <c r="B5" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>130335671</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130335710</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130335807</v>
       </c>
       <c r="B3" t="n">
-        <v>91724</v>
+        <v>91725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130335787</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>130336577</v>
       </c>
       <c r="B5" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>130335671</v>
       </c>
       <c r="B6" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130335710</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130335807</v>
       </c>
       <c r="B3" t="n">
-        <v>91725</v>
+        <v>91726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130335787</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>130335787</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>130335787</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130335710</v>
+        <v>130335807</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hässjemossen, Hässjemossen, Vstm</t>
+          <t>Lofallskullen, Lofallskullen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497279</v>
+        <v>497270</v>
       </c>
       <c r="R2" t="n">
-        <v>6587810</v>
+        <v>6587896</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +746,14 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:57</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,69 +762,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130335807</v>
+        <v>130335787</v>
       </c>
       <c r="B3" t="n">
-        <v>91726</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lofallskullen, Lofallskullen, Vstm</t>
+          <t>Hässjemossen, Hässjemossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497270</v>
+        <v>497328</v>
       </c>
       <c r="R3" t="n">
-        <v>6587896</v>
+        <v>6587874</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,14 +854,24 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,29 +880,53 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130335787</v>
+        <v>130335710</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,7 +954,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497328</v>
+        <v>497279</v>
       </c>
       <c r="R4" t="n">
-        <v>6587874</v>
+        <v>6587810</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,51 +1019,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130336577</v>
+        <v>130335671</v>
       </c>
       <c r="B5" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497453</v>
+        <v>497291</v>
       </c>
       <c r="R5" t="n">
-        <v>6587634</v>
+        <v>6587789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130335671</v>
+        <v>130336577</v>
       </c>
       <c r="B6" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497291</v>
+        <v>497453</v>
       </c>
       <c r="R6" t="n">
-        <v>6587789</v>
+        <v>6587634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,6 +1256,123 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130006474</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartnoppamossen, Svartnoppamossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>497462</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6587496</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56950-2025 artfynd.xlsx
+++ b/artfynd/A 56950-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335807</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335787</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130335671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130336577</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,8 +1403,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130006474</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>